--- a/public/routers/A0_Sistema_FV/A62_Aislado_de_la_red/FV01_Autoconsumos.xlsx
+++ b/public/routers/A0_Sistema_FV/A62_Aislado_de_la_red/FV01_Autoconsumos.xlsx
@@ -1201,7 +1201,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Variable_Ud</t>
+          <t>Ud</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/public/routers/A0_Sistema_FV/A62_Aislado_de_la_red/FV01_Autoconsumos.xlsx
+++ b/public/routers/A0_Sistema_FV/A62_Aislado_de_la_red/FV01_Autoconsumos.xlsx
@@ -1201,7 +1201,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Ud</t>
+          <t>Variable_Ud</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
